--- a/data/trans_bre/P16A09-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A09-Provincia-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 5,08</t>
+          <t>-1,59; 4,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,62</t>
+          <t>-1,16; 4,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 5,03</t>
+          <t>-0,67; 5,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,04</t>
+          <t>1,63; 4,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,84; 316,74</t>
+          <t>-43,57; 297,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,5; 527,99</t>
+          <t>-54,45; 455,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 536,24</t>
+          <t>-29,76; 537,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,93</t>
+          <t>2,65; 7,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 4,72</t>
+          <t>-0,47; 4,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,49</t>
+          <t>-0,18; 3,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,37</t>
+          <t>-0,02; 2,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>102,56; 1581,13</t>
+          <t>142,08; 1885,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 269,51</t>
+          <t>-15,19; 306,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 486,98</t>
+          <t>-21,08; 493,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 1032,14</t>
+          <t>-25,66; 1447,58</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,29</t>
+          <t>-0,72; 3,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,63</t>
+          <t>1,61; 7,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,44</t>
+          <t>-1,43; 3,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,01</t>
+          <t>0,61; 4,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,19; 588,15</t>
+          <t>-53,08; 725,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,97; 1334,47</t>
+          <t>39,98; 1186,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-46,73; 251,62</t>
+          <t>-51,34; 239,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 480,55</t>
+          <t>5,05; 560,66</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 4,59</t>
+          <t>-0,33; 4,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,08</t>
+          <t>0,86; 7,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 4,88</t>
+          <t>-0,08; 5,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 3,23</t>
+          <t>-2,82; 3,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 473,91</t>
+          <t>-21,17; 496,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 332,99</t>
+          <t>8,76; 371,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 603,2</t>
+          <t>-16,19; 553,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,49; 163,85</t>
+          <t>-55,68; 169,84</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 11,51</t>
+          <t>0,55; 11,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 10,82</t>
+          <t>1,44; 11,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 10,26</t>
+          <t>2,94; 10,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,79</t>
+          <t>1,39; 5,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 471,99</t>
+          <t>1,58; 531,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,17; 553,53</t>
+          <t>11,23; 570,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>24,06; —</t>
+          <t>27,14; —</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,47</t>
+          <t>-0,95; 4,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 7,49</t>
+          <t>0,59; 6,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 6,23</t>
+          <t>0,02; 6,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,63</t>
+          <t>0,67; 5,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,04; 491,94</t>
+          <t>-33,4; 515,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,49; 692,91</t>
+          <t>-2,94; 568,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 792,72</t>
+          <t>-22,19; 804,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,91; 347,5</t>
+          <t>12,78; 334,0</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,9</t>
+          <t>-2,4; 1,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,45</t>
+          <t>1,61; 5,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 3,75</t>
+          <t>0,02; 3,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 3,03</t>
+          <t>-1,0; 3,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-50,18; 68,9</t>
+          <t>-46,15; 63,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,76; 759,98</t>
+          <t>62,96; 785,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 446,84</t>
+          <t>-2,26; 412,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-35,77; 183,61</t>
+          <t>-29,8; 191,14</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,75</t>
+          <t>0,39; 5,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,72</t>
+          <t>2,82; 6,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,96</t>
+          <t>1,93; 4,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,4; 12,69</t>
+          <t>7,44; 13,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,82; 143,63</t>
+          <t>5,7; 149,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>113,39; 854,47</t>
+          <t>121,71; 834,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,26; 3486,15</t>
+          <t>95,52; 3887,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>240,47; 1342,05</t>
+          <t>240,69; 1333,71</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,08</t>
+          <t>1,18; 3,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,68</t>
+          <t>2,8; 4,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,27</t>
+          <t>1,66; 3,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,25</t>
+          <t>2,25; 4,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,77; 123,17</t>
+          <t>34,83; 123,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>112,72; 268,35</t>
+          <t>110,35; 274,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>107,08; 320,14</t>
+          <t>93,59; 309,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>112,42; 307,66</t>
+          <t>115,25; 301,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A09-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A09-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>2,86</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1247,27%</t>
+          <t>1356,9%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 4,85</t>
+          <t>-1,55; 4,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,92</t>
+          <t>-1,11; 5,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,04</t>
+          <t>-0,61; 5,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,71</t>
+          <t>1,65; 4,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,57; 297,1</t>
+          <t>-44,39; 285,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,45; 455,82</t>
+          <t>-50,88; 861,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,76; 537,74</t>
+          <t>-34,76; 607,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>169,9%</t>
+          <t>160,31%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,02</t>
+          <t>2,72; 7,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 4,71</t>
+          <t>-0,48; 4,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,35</t>
+          <t>-0,13; 3,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,43</t>
+          <t>0,01; 2,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>142,08; 1885,98</t>
+          <t>129,03; 1639,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 306,7</t>
+          <t>-15,38; 295,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 493,13</t>
+          <t>-16,73; 435,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 1447,58</t>
+          <t>-20,67; 1259,6</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>2,74</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>151,04%</t>
+          <t>156,65%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,14</t>
+          <t>-0,7; 3,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 7,73</t>
+          <t>1,72; 7,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 3,64</t>
+          <t>-1,2; 3,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,85</t>
+          <t>0,72; 4,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,08; 725,11</t>
+          <t>-47,84; 867,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,98; 1186,23</t>
+          <t>41,94; 1073,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-51,34; 239,33</t>
+          <t>-42,89; 298,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,05; 560,66</t>
+          <t>12,81; 632,01</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>1,91</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>64,37%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 4,49</t>
+          <t>-0,28; 4,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,46</t>
+          <t>1,12; 7,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 5,03</t>
+          <t>0,14; 5,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 3,32</t>
+          <t>-1,15; 4,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 496,35</t>
+          <t>-18,85; 434,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 371,98</t>
+          <t>11,18; 380,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 553,21</t>
+          <t>-8,69; 671,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,68; 169,84</t>
+          <t>-33,5; 293,2</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>2,89</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>458,4%</t>
+          <t>495,07%</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 11,51</t>
+          <t>-0,37; 10,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 11,24</t>
+          <t>1,25; 11,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 10,04</t>
+          <t>2,93; 9,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,05</t>
+          <t>1,0; 4,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 531,74</t>
+          <t>-16,98; 436,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,23; 570,3</t>
+          <t>3,76; 552,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,14; —</t>
+          <t>23,22; —</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>114,01%</t>
+          <t>116,74%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,75</t>
+          <t>-0,9; 4,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,88</t>
+          <t>0,36; 7,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,02; 6,23</t>
+          <t>-0,3; 6,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,7</t>
+          <t>0,67; 5,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,4; 515,82</t>
+          <t>-36,56; 477,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 568,42</t>
+          <t>-6,95; 757,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,19; 804,97</t>
+          <t>-15,21; 857,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,78; 334,0</t>
+          <t>10,53; 348,82</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>2,59</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>119,01%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,88</t>
+          <t>-2,35; 2,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,39</t>
+          <t>1,64; 5,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 3,58</t>
+          <t>0,3; 3,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,06</t>
+          <t>0,86; 4,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-46,15; 63,97</t>
+          <t>-46,96; 72,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,96; 785,78</t>
+          <t>69,79; 872,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 412,77</t>
+          <t>4,46; 476,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-29,8; 191,14</t>
+          <t>25,1; 283,17</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,58</t>
+          <t>8,03</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>484,06%</t>
+          <t>300,74%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 5,08</t>
+          <t>0,19; 4,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,8</t>
+          <t>2,88; 6,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,97</t>
+          <t>1,89; 4,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,44; 13,14</t>
+          <t>6,12; 10,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,7; 149,01</t>
+          <t>3,68; 153,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>121,71; 834,73</t>
+          <t>137,29; 884,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,52; 3887,59</t>
+          <t>80,17; 3825,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>240,69; 1333,71</t>
+          <t>167,17; 511,33</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,34</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>190,69%</t>
+          <t>192,95%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,15</t>
+          <t>1,2; 3,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,7</t>
+          <t>2,84; 4,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,23</t>
+          <t>1,73; 3,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,19</t>
+          <t>2,81; 4,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,83; 123,14</t>
+          <t>34,95; 124,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>110,35; 274,43</t>
+          <t>112,6; 278,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>93,59; 309,86</t>
+          <t>106,21; 296,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>115,25; 301,29</t>
+          <t>127,79; 277,13</t>
         </is>
       </c>
     </row>
